--- a/Supplementary Files/Supplementary_File_SF2.xlsx
+++ b/Supplementary Files/Supplementary_File_SF2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t xml:space="preserve">Note: </t>
   </si>
@@ -70,9 +70,6 @@
     <t>General-purpose</t>
   </si>
   <si>
-    <t>NF</t>
-  </si>
-  <si>
     <t>Specialized</t>
   </si>
   <si>
@@ -115,9 +112,6 @@
     <t>The best result is marked by bold.</t>
   </si>
   <si>
-    <t>Table 3: The size (KiB) of the compressed file is generated by the S-Gzip, S-BZip2, NF, CoGI, NAF, P-Gzip, P-BZip2, and HGC encoders on a DNA corpus that has fifteen benchmark sequences, arranged according to file size.</t>
-  </si>
-  <si>
     <t>O.Size</t>
   </si>
   <si>
@@ -128,6 +122,9 @@
   </si>
   <si>
     <t>Name</t>
+  </si>
+  <si>
+    <t>Table 3: The size (KiB) of the compressed file is generated by the S-Gzip, S-BZip2, CoGI, NAF, P-Gzip, P-BZip2, and HGC encoders on a DNA corpus that has fifteen benchmark sequences, arranged according to file size.</t>
   </si>
 </sst>
 </file>
@@ -742,7 +739,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -804,9 +801,6 @@
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -839,29 +833,29 @@
     <xf numFmtId="3" fontId="1" fillId="0" borderId="15" xfId="50" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="55">
@@ -1211,118 +1205,113 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q29"/>
+  <dimension ref="A1:P29"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="9" style="27" customWidth="1"/>
-    <col min="2" max="2" width="7" style="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" style="27" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.28515625" style="27" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="11.7109375" style="27" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.7109375" style="27" customWidth="1"/>
-    <col min="8" max="10" width="11.7109375" style="27" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.85546875" style="27" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" style="27" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.7109375" style="27" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" style="27" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="10.5703125" style="27" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="27"/>
+    <col min="1" max="1" width="9" style="26" customWidth="1"/>
+    <col min="2" max="2" width="7" style="26" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" style="26" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.28515625" style="26" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" style="26" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.7109375" style="26" customWidth="1"/>
+    <col min="7" max="9" width="11.7109375" style="26" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.85546875" style="26" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" style="26" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.7109375" style="26" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" style="26" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="10.5703125" style="26" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="26"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="31.5" customHeight="1">
-      <c r="A1" s="40" t="s">
-        <v>33</v>
-      </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
+    <row r="1" spans="1:16" ht="31.5" customHeight="1">
+      <c r="A1" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="2"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-    </row>
-    <row r="2" spans="1:17" ht="16.5" thickBot="1">
-      <c r="Q2" s="2"/>
-    </row>
-    <row r="3" spans="1:17">
-      <c r="A3" s="38" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3" s="36" t="s">
-        <v>36</v>
-      </c>
-      <c r="C3" s="38" t="s">
+    </row>
+    <row r="2" spans="1:16" ht="16.5" thickBot="1">
+      <c r="P2" s="2"/>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="41" t="s">
+      <c r="C3" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="41"/>
-      <c r="F3" s="36" t="s">
+      <c r="E3" s="39"/>
+      <c r="F3" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="41" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" s="41"/>
-      <c r="I3" s="41"/>
-      <c r="J3" s="41"/>
-      <c r="K3" s="41"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
+      <c r="J3" s="39"/>
+      <c r="K3" s="12"/>
       <c r="L3" s="12"/>
       <c r="M3" s="12"/>
       <c r="N3" s="12"/>
       <c r="O3" s="12"/>
-      <c r="P3" s="12"/>
-      <c r="Q3" s="2"/>
-    </row>
-    <row r="4" spans="1:17" ht="15" customHeight="1" thickBot="1">
-      <c r="A4" s="39"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="39"/>
-      <c r="D4" s="25" t="s">
+      <c r="P3" s="2"/>
+    </row>
+    <row r="4" spans="1:16" ht="15" customHeight="1" thickBot="1">
+      <c r="A4" s="37"/>
+      <c r="B4" s="35"/>
+      <c r="C4" s="37"/>
+      <c r="D4" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="25" t="s">
+      <c r="F4" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="37"/>
-      <c r="G4" s="25" t="s">
+      <c r="G4" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="H4" s="25" t="s">
+      <c r="H4" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="I4" s="23" t="s">
+      <c r="I4" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="J4" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="K4" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="L4" s="9"/>
-      <c r="M4" s="10"/>
-      <c r="N4" s="9"/>
-      <c r="O4" s="10"/>
-      <c r="P4" s="9"/>
-    </row>
-    <row r="5" spans="1:17">
+      <c r="J4" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="K4" s="9"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="9"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="9"/>
+    </row>
+    <row r="5" spans="1:16">
       <c r="A5" s="16" t="s">
         <v>1</v>
       </c>
       <c r="B5" s="20">
         <v>5</v>
       </c>
-      <c r="C5" s="33">
+      <c r="C5" s="32">
         <v>19</v>
       </c>
       <c r="D5" s="19">
@@ -1332,37 +1321,34 @@
         <v>6</v>
       </c>
       <c r="F5" s="19">
+        <v>6</v>
+      </c>
+      <c r="G5" s="19">
         <v>5</v>
-      </c>
-      <c r="G5" s="19">
-        <v>6</v>
       </c>
       <c r="H5" s="19">
         <v>5</v>
       </c>
       <c r="I5" s="19">
-        <v>5</v>
-      </c>
-      <c r="J5" s="19">
         <v>6</v>
       </c>
-      <c r="K5" s="18">
+      <c r="J5" s="18">
         <v>6</v>
       </c>
+      <c r="K5" s="1"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
-      <c r="P5" s="1"/>
-    </row>
-    <row r="6" spans="1:17">
+    </row>
+    <row r="6" spans="1:16">
       <c r="A6" s="19" t="s">
         <v>2</v>
       </c>
       <c r="B6" s="17">
         <v>6</v>
       </c>
-      <c r="C6" s="31">
+      <c r="C6" s="30">
         <v>43</v>
       </c>
       <c r="D6" s="19">
@@ -1371,38 +1357,35 @@
       <c r="E6" s="16">
         <v>12</v>
       </c>
-      <c r="F6" s="16">
-        <v>11</v>
+      <c r="F6" s="19">
+        <v>12</v>
       </c>
       <c r="G6" s="19">
         <v>12</v>
       </c>
-      <c r="H6" s="19">
+      <c r="H6" s="16">
+        <v>11</v>
+      </c>
+      <c r="I6" s="16">
         <v>12</v>
       </c>
-      <c r="I6" s="16">
-        <v>11</v>
-      </c>
-      <c r="J6" s="16">
+      <c r="J6" s="18">
         <v>12</v>
       </c>
-      <c r="K6" s="18">
-        <v>12</v>
-      </c>
+      <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
-      <c r="P6" s="1"/>
-    </row>
-    <row r="7" spans="1:17">
+    </row>
+    <row r="7" spans="1:16">
       <c r="A7" s="19" t="s">
         <v>3</v>
       </c>
       <c r="B7" s="17">
         <v>6</v>
       </c>
-      <c r="C7" s="31">
+      <c r="C7" s="30">
         <v>72</v>
       </c>
       <c r="D7" s="19">
@@ -1411,38 +1394,35 @@
       <c r="E7" s="16">
         <v>19</v>
       </c>
-      <c r="F7" s="21">
+      <c r="F7" s="19">
+        <v>20</v>
+      </c>
+      <c r="G7" s="19">
         <v>18</v>
       </c>
-      <c r="G7" s="19">
-        <v>20</v>
-      </c>
-      <c r="H7" s="19">
+      <c r="H7" s="16">
         <v>18</v>
       </c>
       <c r="I7" s="16">
         <v>18</v>
       </c>
-      <c r="J7" s="16">
-        <v>18</v>
-      </c>
-      <c r="K7" s="18">
+      <c r="J7" s="18">
         <v>19</v>
       </c>
+      <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
-      <c r="P7" s="1"/>
-    </row>
-    <row r="8" spans="1:17">
+    </row>
+    <row r="8" spans="1:16">
       <c r="A8" s="19" t="s">
         <v>4</v>
       </c>
       <c r="B8" s="17">
         <v>8</v>
       </c>
-      <c r="C8" s="31">
+      <c r="C8" s="30">
         <v>1554</v>
       </c>
       <c r="D8" s="19">
@@ -1451,38 +1431,35 @@
       <c r="E8" s="16">
         <v>419</v>
       </c>
-      <c r="F8" s="21">
-        <v>389</v>
+      <c r="F8" s="19">
+        <v>444</v>
       </c>
       <c r="G8" s="19">
-        <v>444</v>
-      </c>
-      <c r="H8" s="19">
         <v>397</v>
       </c>
+      <c r="H8" s="16">
+        <v>385</v>
+      </c>
       <c r="I8" s="16">
-        <v>385</v>
-      </c>
-      <c r="J8" s="16">
         <v>386</v>
       </c>
-      <c r="K8" s="18">
+      <c r="J8" s="18">
         <v>392</v>
       </c>
+      <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
-      <c r="P8" s="1"/>
-    </row>
-    <row r="9" spans="1:17">
+    </row>
+    <row r="9" spans="1:16">
       <c r="A9" s="19" t="s">
         <v>5</v>
       </c>
       <c r="B9" s="17">
         <v>9</v>
       </c>
-      <c r="C9" s="31">
+      <c r="C9" s="30">
         <v>1629</v>
       </c>
       <c r="D9" s="19">
@@ -1491,38 +1468,35 @@
       <c r="E9" s="16">
         <v>432</v>
       </c>
-      <c r="F9" s="21">
-        <v>408</v>
+      <c r="F9" s="19">
+        <v>448</v>
       </c>
       <c r="G9" s="19">
-        <v>448</v>
-      </c>
-      <c r="H9" s="19">
         <v>405</v>
+      </c>
+      <c r="H9" s="16">
+        <v>396</v>
       </c>
       <c r="I9" s="16">
         <v>396</v>
       </c>
-      <c r="J9" s="16">
-        <v>396</v>
-      </c>
-      <c r="K9" s="18">
+      <c r="J9" s="18">
         <v>399</v>
       </c>
+      <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
-      <c r="P9" s="1"/>
-    </row>
-    <row r="10" spans="1:17">
+    </row>
+    <row r="10" spans="1:16">
       <c r="A10" s="19" t="s">
         <v>6</v>
       </c>
       <c r="B10" s="17">
         <v>9</v>
       </c>
-      <c r="C10" s="31">
+      <c r="C10" s="30">
         <v>3799</v>
       </c>
       <c r="D10" s="19">
@@ -1531,38 +1505,35 @@
       <c r="E10" s="16">
         <v>1007</v>
       </c>
-      <c r="F10" s="21">
-        <v>950</v>
+      <c r="F10" s="19">
+        <v>1099</v>
       </c>
       <c r="G10" s="19">
-        <v>1099</v>
-      </c>
-      <c r="H10" s="19">
         <v>949</v>
       </c>
+      <c r="H10" s="16">
+        <v>927</v>
+      </c>
       <c r="I10" s="16">
-        <v>927</v>
-      </c>
-      <c r="J10" s="16">
         <v>933</v>
       </c>
-      <c r="K10" s="18">
+      <c r="J10" s="18">
         <v>933</v>
       </c>
+      <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
-      <c r="P10" s="1"/>
-    </row>
-    <row r="11" spans="1:17">
+    </row>
+    <row r="11" spans="1:16">
       <c r="A11" s="19" t="s">
         <v>7</v>
       </c>
       <c r="B11" s="17">
         <v>9</v>
       </c>
-      <c r="C11" s="31">
+      <c r="C11" s="30">
         <v>4533</v>
       </c>
       <c r="D11" s="19">
@@ -1571,118 +1542,109 @@
       <c r="E11" s="19">
         <v>1223</v>
       </c>
-      <c r="F11" s="21">
-        <v>1134</v>
+      <c r="F11" s="19">
+        <v>1278</v>
       </c>
       <c r="G11" s="19">
-        <v>1278</v>
-      </c>
-      <c r="H11" s="19">
         <v>1178</v>
       </c>
+      <c r="H11" s="16">
+        <v>1130</v>
+      </c>
       <c r="I11" s="16">
-        <v>1130</v>
-      </c>
-      <c r="J11" s="16">
         <v>1129</v>
       </c>
-      <c r="K11" s="18">
+      <c r="J11" s="18">
         <v>1140</v>
       </c>
+      <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
-      <c r="P11" s="1"/>
-    </row>
-    <row r="12" spans="1:17">
+    </row>
+    <row r="12" spans="1:16">
       <c r="A12" s="19" t="s">
         <v>8</v>
       </c>
       <c r="B12" s="17">
         <v>10</v>
       </c>
-      <c r="C12" s="31">
+      <c r="C12" s="30">
         <v>8777</v>
       </c>
-      <c r="D12" s="28">
+      <c r="D12" s="27">
         <v>2357</v>
       </c>
-      <c r="E12" s="28">
+      <c r="E12" s="27">
         <v>2297</v>
       </c>
-      <c r="F12" s="21">
-        <v>2195</v>
+      <c r="F12" s="19">
+        <v>2355</v>
       </c>
       <c r="G12" s="19">
-        <v>2355</v>
-      </c>
-      <c r="H12" s="19">
         <v>2069</v>
       </c>
+      <c r="H12" s="16">
+        <v>2059</v>
+      </c>
       <c r="I12" s="16">
-        <v>2059</v>
-      </c>
-      <c r="J12" s="16">
         <v>2108</v>
       </c>
-      <c r="K12" s="18">
+      <c r="J12" s="18">
         <v>2073</v>
       </c>
+      <c r="K12" s="1"/>
       <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
-      <c r="N12" s="11"/>
+      <c r="M12" s="11"/>
+      <c r="N12" s="1"/>
       <c r="O12" s="1"/>
-      <c r="P12" s="1"/>
-    </row>
-    <row r="13" spans="1:17">
-      <c r="A13" s="26" t="s">
+    </row>
+    <row r="13" spans="1:16">
+      <c r="A13" s="25" t="s">
         <v>14</v>
       </c>
       <c r="B13" s="17">
         <v>9</v>
       </c>
-      <c r="C13" s="31">
+      <c r="C13" s="30">
         <v>8931</v>
       </c>
-      <c r="D13" s="28">
+      <c r="D13" s="27">
         <v>2547</v>
       </c>
-      <c r="E13" s="28">
+      <c r="E13" s="27">
         <v>2420</v>
       </c>
-      <c r="F13" s="21">
-        <v>2233</v>
+      <c r="F13" s="19">
+        <v>2595</v>
       </c>
       <c r="G13" s="19">
-        <v>2595</v>
-      </c>
-      <c r="H13" s="19">
         <v>2221</v>
       </c>
+      <c r="H13" s="16">
+        <v>2223</v>
+      </c>
       <c r="I13" s="16">
-        <v>2223</v>
-      </c>
-      <c r="J13" s="16">
         <v>2235</v>
       </c>
-      <c r="K13" s="18">
+      <c r="J13" s="18">
         <v>2251</v>
       </c>
+      <c r="K13" s="1"/>
       <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
-      <c r="N13" s="11"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="1"/>
       <c r="O13" s="1"/>
-      <c r="P13" s="1"/>
-    </row>
-    <row r="14" spans="1:17">
+    </row>
+    <row r="14" spans="1:16">
       <c r="A14" s="19" t="s">
         <v>9</v>
       </c>
       <c r="B14" s="17">
         <v>10</v>
       </c>
-      <c r="C14" s="31">
+      <c r="C14" s="30">
         <v>10403</v>
       </c>
       <c r="D14" s="19">
@@ -1691,38 +1653,35 @@
       <c r="E14" s="19">
         <v>2822</v>
       </c>
-      <c r="F14" s="21">
-        <v>2601</v>
+      <c r="F14" s="19">
+        <v>2853</v>
       </c>
       <c r="G14" s="19">
-        <v>2853</v>
-      </c>
-      <c r="H14" s="19">
         <v>2653</v>
       </c>
+      <c r="H14" s="16">
+        <v>2574</v>
+      </c>
       <c r="I14" s="16">
-        <v>2574</v>
-      </c>
-      <c r="J14" s="16">
         <v>2599</v>
       </c>
-      <c r="K14" s="18">
+      <c r="J14" s="18">
         <v>2605</v>
       </c>
+      <c r="K14" s="1"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
-      <c r="P14" s="1"/>
-    </row>
-    <row r="15" spans="1:17">
+    </row>
+    <row r="15" spans="1:16">
       <c r="A15" s="19" t="s">
         <v>10</v>
       </c>
       <c r="B15" s="17">
         <v>10</v>
       </c>
-      <c r="C15" s="31">
+      <c r="C15" s="30">
         <v>25785</v>
       </c>
       <c r="D15" s="19">
@@ -1731,38 +1690,35 @@
       <c r="E15" s="19">
         <v>6931</v>
       </c>
-      <c r="F15" s="21">
-        <v>6447</v>
+      <c r="F15" s="19">
+        <v>7042</v>
       </c>
       <c r="G15" s="19">
-        <v>7042</v>
-      </c>
-      <c r="H15" s="19">
         <v>6011</v>
       </c>
+      <c r="H15" s="16">
+        <v>6306</v>
+      </c>
       <c r="I15" s="16">
-        <v>6306</v>
-      </c>
-      <c r="J15" s="16">
         <v>6372</v>
       </c>
-      <c r="K15" s="18">
+      <c r="J15" s="18">
         <v>6130</v>
       </c>
+      <c r="K15" s="1"/>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
-      <c r="P15" s="1"/>
-    </row>
-    <row r="16" spans="1:17">
+    </row>
+    <row r="16" spans="1:16">
       <c r="A16" s="19" t="s">
         <v>11</v>
       </c>
       <c r="B16" s="17">
         <v>11</v>
       </c>
-      <c r="C16" s="31">
+      <c r="C16" s="30">
         <v>42249</v>
       </c>
       <c r="D16" s="19">
@@ -1771,38 +1727,35 @@
       <c r="E16" s="19">
         <v>11306</v>
       </c>
-      <c r="F16" s="21">
-        <v>10563</v>
+      <c r="F16" s="19">
+        <v>11719</v>
       </c>
       <c r="G16" s="19">
-        <v>11719</v>
-      </c>
-      <c r="H16" s="19">
         <v>9759</v>
       </c>
+      <c r="H16" s="16">
+        <v>10432</v>
+      </c>
       <c r="I16" s="16">
-        <v>10432</v>
-      </c>
-      <c r="J16" s="16">
         <v>10425</v>
       </c>
-      <c r="K16" s="18">
+      <c r="J16" s="18">
         <v>10063</v>
       </c>
+      <c r="K16" s="1"/>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
-      <c r="P16" s="1"/>
-    </row>
-    <row r="17" spans="1:17">
+    </row>
+    <row r="17" spans="1:16">
       <c r="A17" s="19" t="s">
         <v>12</v>
       </c>
       <c r="B17" s="17">
         <v>11</v>
       </c>
-      <c r="C17" s="31">
+      <c r="C17" s="30">
         <v>61099</v>
       </c>
       <c r="D17" s="19">
@@ -1811,38 +1764,35 @@
       <c r="E17" s="19">
         <v>15733</v>
       </c>
-      <c r="F17" s="21">
-        <v>15275</v>
+      <c r="F17" s="19">
+        <v>16685</v>
       </c>
       <c r="G17" s="19">
-        <v>16685</v>
-      </c>
-      <c r="H17" s="19">
         <v>13138</v>
       </c>
+      <c r="H17" s="16">
+        <v>14523</v>
+      </c>
       <c r="I17" s="16">
-        <v>14523</v>
-      </c>
-      <c r="J17" s="16">
         <v>14559</v>
       </c>
-      <c r="K17" s="18">
+      <c r="J17" s="18">
         <v>13673</v>
       </c>
+      <c r="K17" s="1"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
-      <c r="P17" s="1"/>
-    </row>
-    <row r="18" spans="1:17">
+    </row>
+    <row r="18" spans="1:16">
       <c r="A18" s="19" t="s">
         <v>15</v>
       </c>
       <c r="B18" s="17">
         <v>12</v>
       </c>
-      <c r="C18" s="31">
+      <c r="C18" s="30">
         <v>138858</v>
       </c>
       <c r="D18" s="19">
@@ -1851,38 +1801,35 @@
       <c r="E18" s="19">
         <v>36373</v>
       </c>
-      <c r="F18" s="21">
-        <v>34715</v>
+      <c r="F18" s="19">
+        <v>33969</v>
       </c>
       <c r="G18" s="19">
-        <v>33969</v>
-      </c>
-      <c r="H18" s="19">
         <v>33553</v>
       </c>
+      <c r="H18" s="16">
+        <v>33811</v>
+      </c>
       <c r="I18" s="16">
-        <v>33811</v>
-      </c>
-      <c r="J18" s="16">
         <v>33399</v>
       </c>
-      <c r="K18" s="18">
+      <c r="J18" s="18">
         <v>31214</v>
       </c>
+      <c r="K18" s="1"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
-      <c r="P18" s="1"/>
-    </row>
-    <row r="19" spans="1:17" ht="16.5" thickBot="1">
-      <c r="A19" s="24" t="s">
+    </row>
+    <row r="19" spans="1:16" ht="16.5" thickBot="1">
+      <c r="A19" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="B19" s="22">
+      <c r="B19" s="21">
         <v>12</v>
       </c>
-      <c r="C19" s="32">
+      <c r="C19" s="31">
         <v>185306</v>
       </c>
       <c r="D19" s="16">
@@ -1891,33 +1838,30 @@
       <c r="E19" s="16">
         <v>47623</v>
       </c>
-      <c r="F19" s="21">
-        <v>46327</v>
+      <c r="F19" s="19">
+        <v>50750</v>
       </c>
       <c r="G19" s="19">
-        <v>50750</v>
-      </c>
-      <c r="H19" s="19">
         <v>42732</v>
       </c>
+      <c r="H19" s="16">
+        <v>44248</v>
+      </c>
       <c r="I19" s="16">
-        <v>44248</v>
-      </c>
-      <c r="J19" s="16">
         <v>43816</v>
       </c>
-      <c r="K19" s="18">
+      <c r="J19" s="18">
         <v>42010</v>
       </c>
+      <c r="K19" s="1"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
-      <c r="P19" s="1"/>
-    </row>
-    <row r="20" spans="1:17" ht="16.5" thickBot="1">
+    </row>
+    <row r="20" spans="1:16" ht="16.5" thickBot="1">
       <c r="A20" s="15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B20" s="14"/>
       <c r="C20" s="13">
@@ -1925,7 +1869,7 @@
         <v>493057</v>
       </c>
       <c r="D20" s="13">
-        <f t="shared" ref="D20:K20" si="0">SUM(D5:D19)</f>
+        <f t="shared" ref="D20:J20" si="0">SUM(D5:D19)</f>
         <v>135069</v>
       </c>
       <c r="E20" s="13">
@@ -1934,53 +1878,48 @@
       </c>
       <c r="F20" s="13">
         <f t="shared" si="0"/>
-        <v>123271</v>
+        <v>131275</v>
       </c>
       <c r="G20" s="13">
         <f t="shared" si="0"/>
-        <v>131275</v>
+        <v>115100</v>
       </c>
       <c r="H20" s="13">
         <f t="shared" si="0"/>
-        <v>115100</v>
+        <v>119048</v>
       </c>
       <c r="I20" s="13">
         <f t="shared" si="0"/>
-        <v>119048</v>
-      </c>
-      <c r="J20" s="13">
-        <f t="shared" si="0"/>
         <v>118393</v>
       </c>
-      <c r="K20" s="29">
+      <c r="J20" s="28">
         <f t="shared" si="0"/>
         <v>112920</v>
       </c>
-      <c r="L20" s="7"/>
-      <c r="M20" s="4"/>
+      <c r="K20" s="7"/>
+      <c r="L20" s="4"/>
+      <c r="M20" s="7"/>
       <c r="N20" s="7"/>
-      <c r="O20" s="7"/>
-      <c r="P20" s="4"/>
-    </row>
-    <row r="21" spans="1:17">
+      <c r="O20" s="4"/>
+    </row>
+    <row r="21" spans="1:16">
       <c r="A21" s="5"/>
       <c r="B21" s="4"/>
       <c r="C21" s="7"/>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="7"/>
-      <c r="I21" s="4"/>
-      <c r="J21" s="7"/>
-      <c r="K21" s="4"/>
-      <c r="L21" s="7"/>
-      <c r="M21" s="4"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="7"/>
+      <c r="J21" s="4"/>
+      <c r="K21" s="7"/>
+      <c r="L21" s="4"/>
+      <c r="M21" s="7"/>
       <c r="N21" s="7"/>
-      <c r="O21" s="7"/>
-      <c r="P21" s="4"/>
-    </row>
-    <row r="22" spans="1:17">
+      <c r="O21" s="4"/>
+    </row>
+    <row r="22" spans="1:16">
       <c r="A22" s="5" t="s">
         <v>0</v>
       </c>
@@ -1990,130 +1929,123 @@
       <c r="E22" s="8"/>
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="3"/>
-      <c r="J22" s="8"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="16"/>
       <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-    </row>
-    <row r="23" spans="1:17">
-      <c r="A23" s="34" t="s">
+    </row>
+    <row r="23" spans="1:16">
+      <c r="A23" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="B23" s="34"/>
-      <c r="C23" s="34"/>
-      <c r="D23" s="34"/>
-      <c r="E23" s="34"/>
-      <c r="F23" s="34"/>
-      <c r="G23" s="34"/>
-      <c r="H23" s="34"/>
-      <c r="I23" s="34"/>
-      <c r="J23" s="34"/>
-      <c r="K23" s="34"/>
-      <c r="L23" s="30"/>
-    </row>
-    <row r="24" spans="1:17">
-      <c r="A24" s="34" t="s">
-        <v>32</v>
-      </c>
-      <c r="B24" s="34"/>
-      <c r="C24" s="34"/>
-      <c r="D24" s="34"/>
-      <c r="E24" s="34"/>
-      <c r="F24" s="34"/>
-      <c r="G24" s="34"/>
-      <c r="H24" s="34"/>
-      <c r="I24" s="34"/>
-      <c r="J24" s="34"/>
-      <c r="K24" s="34"/>
-      <c r="L24" s="34"/>
-      <c r="M24" s="34"/>
-      <c r="N24" s="34"/>
-      <c r="O24" s="34"/>
-      <c r="P24" s="34"/>
-      <c r="Q24" s="34"/>
-    </row>
-    <row r="25" spans="1:17">
-      <c r="A25" s="34" t="s">
-        <v>27</v>
-      </c>
-      <c r="B25" s="34"/>
-      <c r="C25" s="34"/>
-      <c r="D25" s="34"/>
-      <c r="E25" s="34"/>
+      <c r="B23" s="40"/>
+      <c r="C23" s="40"/>
+      <c r="D23" s="40"/>
+      <c r="E23" s="40"/>
+      <c r="F23" s="40"/>
+      <c r="G23" s="40"/>
+      <c r="H23" s="40"/>
+      <c r="I23" s="40"/>
+      <c r="J23" s="40"/>
+      <c r="K23" s="40"/>
+      <c r="L23" s="40"/>
+    </row>
+    <row r="24" spans="1:16">
+      <c r="A24" s="40" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="40"/>
+      <c r="C24" s="40"/>
+      <c r="D24" s="40"/>
+      <c r="E24" s="40"/>
+      <c r="F24" s="40"/>
+      <c r="G24" s="40"/>
+      <c r="H24" s="40"/>
+      <c r="I24" s="40"/>
+      <c r="J24" s="40"/>
+      <c r="K24" s="40"/>
+      <c r="L24" s="40"/>
+      <c r="M24" s="40"/>
+      <c r="N24" s="40"/>
+      <c r="O24" s="40"/>
+      <c r="P24" s="40"/>
+    </row>
+    <row r="25" spans="1:16">
+      <c r="A25" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" s="40"/>
+      <c r="C25" s="40"/>
+      <c r="D25" s="40"/>
+      <c r="E25" s="40"/>
       <c r="F25" s="16"/>
       <c r="G25" s="16"/>
       <c r="H25" s="16"/>
-      <c r="I25" s="16"/>
-    </row>
-    <row r="26" spans="1:17">
-      <c r="A26" s="34" t="s">
-        <v>28</v>
-      </c>
-      <c r="B26" s="34"/>
-      <c r="C26" s="34"/>
-      <c r="D26" s="34"/>
+    </row>
+    <row r="26" spans="1:16">
+      <c r="A26" s="40" t="s">
+        <v>27</v>
+      </c>
+      <c r="B26" s="40"/>
+      <c r="C26" s="40"/>
+      <c r="D26" s="40"/>
       <c r="E26" s="16"/>
       <c r="F26" s="16"/>
       <c r="G26" s="16"/>
       <c r="H26" s="16"/>
-      <c r="I26" s="16"/>
-    </row>
-    <row r="27" spans="1:17">
-      <c r="A27" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="B27" s="35"/>
-      <c r="E27" s="30"/>
-      <c r="F27" s="30"/>
-      <c r="G27" s="30"/>
-      <c r="H27" s="30"/>
-      <c r="I27" s="30"/>
-    </row>
-    <row r="28" spans="1:17">
-      <c r="A28" s="35" t="s">
+    </row>
+    <row r="27" spans="1:16">
+      <c r="A27" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="B28" s="35"/>
-      <c r="C28" s="35"/>
-      <c r="D28" s="35"/>
-    </row>
-    <row r="29" spans="1:17">
-      <c r="A29" s="34" t="s">
+      <c r="B27" s="33"/>
+      <c r="C27" s="27"/>
+      <c r="E27" s="29"/>
+      <c r="F27" s="29"/>
+      <c r="G27" s="29"/>
+      <c r="H27" s="29"/>
+    </row>
+    <row r="28" spans="1:16">
+      <c r="A28" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="B29" s="34"/>
-      <c r="C29" s="34"/>
-      <c r="D29" s="34"/>
-      <c r="E29" s="34"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="8"/>
-      <c r="H29" s="7"/>
-      <c r="I29" s="8"/>
-      <c r="J29" s="7"/>
-      <c r="K29" s="8"/>
-      <c r="L29" s="7"/>
-      <c r="M29" s="8"/>
+      <c r="B28" s="33"/>
+      <c r="C28" s="33"/>
+      <c r="D28" s="33"/>
+      <c r="E28" s="27"/>
+    </row>
+    <row r="29" spans="1:16">
+      <c r="A29" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="40"/>
+      <c r="C29" s="40"/>
+      <c r="D29" s="40"/>
+      <c r="E29" s="40"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="7"/>
+      <c r="H29" s="8"/>
+      <c r="I29" s="7"/>
+      <c r="J29" s="8"/>
+      <c r="K29" s="7"/>
+      <c r="L29" s="8"/>
+      <c r="M29" s="7"/>
       <c r="N29" s="7"/>
-      <c r="O29" s="7"/>
-      <c r="P29" s="8"/>
+      <c r="O29" s="8"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="G3:K3"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A23:K23"/>
+  <mergeCells count="11">
     <mergeCell ref="A25:E25"/>
     <mergeCell ref="A26:D26"/>
     <mergeCell ref="A29:E29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="A24:Q24"/>
+    <mergeCell ref="A24:P24"/>
+    <mergeCell ref="A23:L23"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="F3:J3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="A3:A4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
